--- a/artfynd/A 40437-2025 artfynd.xlsx
+++ b/artfynd/A 40437-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128754036</v>
+        <v>136865950</v>
       </c>
       <c r="B2" t="n">
-        <v>57950</v>
+        <v>91889</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,45 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>3215</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Brandserud, Brandserud, Vrm</t>
+          <t>Barlingshultsälven, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>348109</v>
+        <v>348106</v>
       </c>
       <c r="R2" t="n">
-        <v>6599890</v>
+        <v>6599862</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,27 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Hördes i flykt 3 gånger, sedan syntes den flyga här. Såg ett stort hålhack i närheten.</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,27 +775,27 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jens Johansen</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jesper Granback, Anna Meijerhöffer</t>
+          <t>Jens Johansen, Jesper Granback</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128754036</t>
+          <t>https://artportalen.se/Sighting/136865950</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128752933</v>
+        <v>128754036</v>
       </c>
       <c r="B3" t="n">
-        <v>97983</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,27 +803,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -844,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>347987</v>
+        <v>348109</v>
       </c>
       <c r="R3" t="n">
-        <v>6599913</v>
+        <v>6599890</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,7 +880,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Hördes i flykt 3 gånger, sedan syntes den flyga här. Såg ett stort hålhack i närheten.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,7 +894,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -910,13 +905,363 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jesper Granback, Anna Meijerhöffer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/128754036</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136865949</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99270</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Barlingshultsälven, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>347930</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6599931</v>
+      </c>
+      <c r="S4" t="n">
+        <v>6</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Silbodal</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jens Johansen, Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136865949</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128752933</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Brandserud, Brandserud, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>347987</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6599913</v>
+      </c>
+      <c r="S5" t="n">
+        <v>8</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Silbodal</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/128752933</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136865961</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98215</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Barlingshultsälven, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>348204</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6599797</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Glava</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jens Johansen, Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136865961</t>
         </is>
       </c>
     </row>
@@ -924,6 +1269,9 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40437-2025 artfynd.xlsx
+++ b/artfynd/A 40437-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136865950</v>
       </c>
       <c r="B2" t="n">
-        <v>91889</v>
+        <v>91891</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>136865949</v>
       </c>
       <c r="B4" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>136865961</v>
       </c>
       <c r="B6" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 40437-2025 artfynd.xlsx
+++ b/artfynd/A 40437-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136865950</v>
       </c>
       <c r="B2" t="n">
-        <v>91891</v>
+        <v>91893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>136865949</v>
       </c>
       <c r="B4" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>136865961</v>
       </c>
       <c r="B6" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 40437-2025 artfynd.xlsx
+++ b/artfynd/A 40437-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136865950</v>
       </c>
       <c r="B2" t="n">
-        <v>91893</v>
+        <v>91894</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>136865949</v>
       </c>
       <c r="B4" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>136865961</v>
       </c>
       <c r="B6" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 40437-2025 artfynd.xlsx
+++ b/artfynd/A 40437-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136865950</v>
       </c>
       <c r="B2" t="n">
-        <v>91894</v>
+        <v>91900</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>136865949</v>
       </c>
       <c r="B4" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>136865961</v>
       </c>
       <c r="B6" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 40437-2025 artfynd.xlsx
+++ b/artfynd/A 40437-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136865950</v>
       </c>
       <c r="B2" t="n">
-        <v>91900</v>
+        <v>91904</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>136865949</v>
       </c>
       <c r="B4" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>136865961</v>
       </c>
       <c r="B6" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 40437-2025 artfynd.xlsx
+++ b/artfynd/A 40437-2025 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>136865949</v>
       </c>
       <c r="B4" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>136865961</v>
       </c>
       <c r="B6" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 40437-2025 artfynd.xlsx
+++ b/artfynd/A 40437-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136865950</v>
       </c>
       <c r="B2" t="n">
-        <v>91904</v>
+        <v>91906</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>136865949</v>
       </c>
       <c r="B4" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>136865961</v>
       </c>
       <c r="B6" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 40437-2025 artfynd.xlsx
+++ b/artfynd/A 40437-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136865950</v>
       </c>
       <c r="B2" t="n">
-        <v>91906</v>
+        <v>91919</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>136865949</v>
       </c>
       <c r="B4" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>136865961</v>
       </c>
       <c r="B6" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 40437-2025 artfynd.xlsx
+++ b/artfynd/A 40437-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136865950</v>
       </c>
       <c r="B2" t="n">
-        <v>91919</v>
+        <v>91921</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>136865949</v>
       </c>
       <c r="B4" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>136865961</v>
       </c>
       <c r="B6" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 40437-2025 artfynd.xlsx
+++ b/artfynd/A 40437-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136865950</v>
       </c>
       <c r="B2" t="n">
-        <v>91921</v>
+        <v>91924</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>136865949</v>
       </c>
       <c r="B4" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>136865961</v>
       </c>
       <c r="B6" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 40437-2025 artfynd.xlsx
+++ b/artfynd/A 40437-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136865950</v>
       </c>
       <c r="B2" t="n">
-        <v>91924</v>
+        <v>91934</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>136865949</v>
       </c>
       <c r="B4" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>136865961</v>
       </c>
       <c r="B6" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 40437-2025 artfynd.xlsx
+++ b/artfynd/A 40437-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136865950</v>
       </c>
       <c r="B2" t="n">
-        <v>91934</v>
+        <v>91935</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>136865949</v>
       </c>
       <c r="B4" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>136865961</v>
       </c>
       <c r="B6" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 40437-2025 artfynd.xlsx
+++ b/artfynd/A 40437-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136865950</v>
       </c>
       <c r="B2" t="n">
-        <v>91935</v>
+        <v>91938</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>136865949</v>
       </c>
       <c r="B4" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>136865961</v>
       </c>
       <c r="B6" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 40437-2025 artfynd.xlsx
+++ b/artfynd/A 40437-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136865950</v>
       </c>
       <c r="B2" t="n">
-        <v>91938</v>
+        <v>91940</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>136865949</v>
       </c>
       <c r="B4" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>136865961</v>
       </c>
       <c r="B6" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 40437-2025 artfynd.xlsx
+++ b/artfynd/A 40437-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136865950</v>
       </c>
       <c r="B2" t="n">
-        <v>91940</v>
+        <v>91945</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>136865949</v>
       </c>
       <c r="B4" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>136865961</v>
       </c>
       <c r="B6" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 40437-2025 artfynd.xlsx
+++ b/artfynd/A 40437-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136865950</v>
       </c>
       <c r="B2" t="n">
-        <v>91945</v>
+        <v>91957</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>136865949</v>
       </c>
       <c r="B4" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>136865961</v>
       </c>
       <c r="B6" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
